--- a/backend/storage/imports/Master_SBM/19. SATUAN BIAYA PENYELENGGARAAN PERWAKILAN REPUBLIK INDONESIA DI LUAR NEGERI.xlsx
+++ b/backend/storage/imports/Master_SBM/19. SATUAN BIAYA PENYELENGGARAAN PERWAKILAN REPUBLIK INDONESIA DI LUAR NEGERI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E84D4B-42CD-4B44-A8C9-CDD5BABCE8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9FDE20-07F4-4C6E-AD63-EB39DB786130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4761CDB3-D481-42D7-A8EA-191E94B31355}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="181">
   <si>
     <t>(dalam  US$)</t>
   </si>
@@ -541,13 +541,43 @@
     <t>Pemeliharaan, Pengadaan Inventaris Kantor, Pakaian Sopir/Satpam, Sewa Kendaraan, dan Konsumsi Rapat</t>
   </si>
   <si>
-    <t>Pemeliharaan</t>
-  </si>
-  <si>
     <t>Pengadaan Inventaris Kantor  (OT)</t>
   </si>
   <si>
     <t>Pakaian Sopir/ Satpam (Stel)</t>
+  </si>
+  <si>
+    <t>Konsumsi Rapat (OK)</t>
+  </si>
+  <si>
+    <t>New  York</t>
+  </si>
+  <si>
+    <t>AMERIKA  SELATAN</t>
+  </si>
+  <si>
+    <t>Kopenhagen</t>
+  </si>
+  <si>
+    <t>Helsinki</t>
+  </si>
+  <si>
+    <t>Lisbon</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>Bandar  Seri Bagawan</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>SATUAN BIAYA PENYELENGGARAAN PERWAKILAN REPUBLIK INDONESIA DI LUAR NEGERI</t>
+  </si>
+  <si>
+    <t>Pemeliharaan Kendaraan dinas  (Unit/ Tahun)</t>
   </si>
   <si>
     <r>
@@ -556,24 +586,7 @@
         <rFont val="Cambria"/>
         <family val="1"/>
       </rPr>
-      <t>Sewa  kendaraan
-(hari)</t>
-    </r>
-  </si>
-  <si>
-    <t>Konsumsi Rapat (OK)</t>
-  </si>
-  <si>
-    <t>Kendaraan dinas  (Unit/ Tahun)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <rFont val="Cambria"/>
-        <family val="1"/>
-      </rPr>
-      <t>Gedung (m</t>
+      <t>Pemeliharaan Gedung (m</t>
     </r>
     <r>
       <rPr>
@@ -600,7 +613,7 @@
         <rFont val="Cambria"/>
         <family val="1"/>
       </rPr>
-      <t>Halaman (m</t>
+      <t>Pemeliharaan Halaman (m</t>
     </r>
     <r>
       <rPr>
@@ -621,40 +634,16 @@
     </r>
   </si>
   <si>
-    <t>Sedan</t>
-  </si>
-  <si>
-    <t>Bus</t>
-  </si>
-  <si>
-    <t>Mobil Box</t>
-  </si>
-  <si>
-    <t>New  York</t>
-  </si>
-  <si>
-    <t>AMERIKA  SELATAN</t>
-  </si>
-  <si>
-    <t>Kopenhagen</t>
-  </si>
-  <si>
-    <t>Helsinki</t>
-  </si>
-  <si>
-    <t>Lisbon</t>
-  </si>
-  <si>
-    <t>Roma</t>
-  </si>
-  <si>
-    <t>Bandar  Seri Bagawan</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>SATUAN BIAYA PENYELENGGARAAN PERWAKILAN REPUBLIK INDONESIA DI LUAR NEGERI</t>
+    <t>Sewa  kendaraan
+Bus (hari)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sewa  kendaraan
+Sedan (hari) </t>
+  </si>
+  <si>
+    <t>Sewa  kendaraan
+Mobil Box (hari)</t>
   </si>
 </sst>
 </file>
@@ -706,7 +695,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -751,61 +740,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -861,30 +800,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -893,6 +808,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1208,10 +1126,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE13D45E-6403-4E30-8793-FB03B42EFE1D}">
-  <dimension ref="A1:K313"/>
+  <dimension ref="A1:K312"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="40.44140625" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
     <col min="4" max="4" width="17.88671875" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
@@ -1224,7 +1143,7 @@
         <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -1313,28 +1232,28 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>181</v>
+      <c r="C6" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1599,28 +1518,28 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F17" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G17" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>181</v>
+      <c r="C17" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -1833,28 +1752,28 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E26" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F26" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G26" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H26" s="29" t="s">
-        <v>181</v>
+      <c r="C26" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -1937,28 +1856,28 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D30" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E30" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F30" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G30" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H30" s="29" t="s">
-        <v>181</v>
+      <c r="C30" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -2275,28 +2194,28 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C43" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D43" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E43" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F43" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G43" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H43" s="29" t="s">
-        <v>181</v>
+      <c r="C43" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F43" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G43" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H43" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
@@ -2431,28 +2350,28 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C49" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D49" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E49" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F49" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G49" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H49" s="29" t="s">
-        <v>181</v>
+      <c r="C49" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F49" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G49" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H49" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
@@ -2665,28 +2584,28 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C58" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D58" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E58" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F58" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G58" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H58" s="29" t="s">
-        <v>181</v>
+      <c r="C58" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F58" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G58" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H58" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
@@ -2899,28 +2818,28 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C67" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D67" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E67" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F67" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G67" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H67" s="29" t="s">
-        <v>181</v>
+      <c r="C67" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E67" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F67" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G67" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H67" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -3003,28 +2922,28 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C71" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D71" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E71" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F71" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G71" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H71" s="29" t="s">
-        <v>181</v>
+      <c r="C71" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E71" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F71" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G71" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H71" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
@@ -3159,28 +3078,28 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B77" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C77" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D77" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E77" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F77" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G77" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H77" s="29" t="s">
-        <v>181</v>
+      <c r="C77" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D77" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E77" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F77" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G77" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H77" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
@@ -3315,28 +3234,28 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B83" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="C83" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D83" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E83" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F83" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G83" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H83" s="29" t="s">
-        <v>181</v>
+      <c r="C83" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D83" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E83" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F83" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G83" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H83" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
@@ -3497,28 +3416,28 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C90" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D90" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E90" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F90" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G90" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H90" s="29" t="s">
-        <v>181</v>
+      <c r="C90" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D90" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E90" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F90" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G90" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H90" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
@@ -3913,28 +3832,28 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="C106" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D106" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E106" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F106" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G106" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H106" s="29" t="s">
-        <v>181</v>
+      <c r="C106" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D106" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E106" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F106" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G106" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H106" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
@@ -4017,28 +3936,28 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B110" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C110" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D110" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E110" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F110" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G110" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H110" s="29" t="s">
-        <v>181</v>
+      <c r="C110" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D110" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E110" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F110" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G110" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H110" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
@@ -4251,28 +4170,28 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C119" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D119" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E119" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F119" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G119" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H119" s="29" t="s">
-        <v>181</v>
+      <c r="C119" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D119" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E119" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F119" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G119" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H119" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
@@ -4485,28 +4404,28 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B128" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="C128" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D128" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E128" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F128" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G128" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H128" s="29" t="s">
-        <v>181</v>
+      <c r="C128" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D128" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E128" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F128" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G128" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H128" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
@@ -4953,28 +4872,28 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B146" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C146" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D146" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E146" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F146" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G146" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H146" s="29" t="s">
-        <v>181</v>
+      <c r="C146" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D146" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E146" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F146" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G146" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H146" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.3">
@@ -5291,209 +5210,227 @@
       <c r="H159" s="18"/>
       <c r="I159" s="18"/>
       <c r="J159" s="18"/>
-      <c r="K159" s="28" t="s">
+      <c r="K159" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="19" t="s">
+    <row r="160" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B160" s="19" t="s">
+      <c r="B160" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C160" s="20" t="s">
+      <c r="C160" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="E160" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F160" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="D160" s="21"/>
-      <c r="E160" s="22"/>
-      <c r="F160" s="19" t="s">
+      <c r="G160" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="G160" s="19" t="s">
+      <c r="H160" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="I160" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="J160" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="K160" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="H160" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="I160" s="24"/>
-      <c r="J160" s="25"/>
-      <c r="K160" s="19" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A161" s="26"/>
-      <c r="B161" s="26"/>
-      <c r="C161" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D161" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="E161" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F161" s="26"/>
-      <c r="G161" s="26"/>
-      <c r="H161" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="I161" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="J161" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="K161" s="26"/>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A161" s="10">
+        <v>-1</v>
+      </c>
+      <c r="B161" s="10">
+        <v>-2</v>
+      </c>
+      <c r="C161" s="10">
+        <v>-3</v>
+      </c>
+      <c r="D161" s="10">
+        <v>-4</v>
+      </c>
+      <c r="E161" s="10">
+        <v>-5</v>
+      </c>
+      <c r="F161" s="10">
+        <v>-6</v>
+      </c>
+      <c r="G161" s="10">
+        <v>-7</v>
+      </c>
+      <c r="H161" s="10">
+        <v>-8</v>
+      </c>
+      <c r="I161" s="10">
+        <v>-9</v>
+      </c>
+      <c r="J161" s="10">
+        <v>-10</v>
+      </c>
+      <c r="K161" s="10">
+        <v>-11</v>
+      </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A162" s="10">
-        <v>-1</v>
-      </c>
-      <c r="B162" s="10">
-        <v>-2</v>
-      </c>
-      <c r="C162" s="10">
-        <v>-3</v>
-      </c>
-      <c r="D162" s="10">
-        <v>-4</v>
-      </c>
-      <c r="E162" s="10">
-        <v>-5</v>
-      </c>
-      <c r="F162" s="10">
-        <v>-6</v>
-      </c>
-      <c r="G162" s="10">
-        <v>-7</v>
-      </c>
-      <c r="H162" s="10">
-        <v>-8</v>
-      </c>
-      <c r="I162" s="10">
-        <v>-9</v>
-      </c>
-      <c r="J162" s="10">
-        <v>-10</v>
-      </c>
-      <c r="K162" s="10">
-        <v>-11</v>
+      <c r="A162" s="9"/>
+      <c r="B162" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C162" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D162" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E162" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F162" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G162" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H162" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I162" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J162" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K162" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A163" s="9"/>
+      <c r="A163" s="13">
+        <v>1</v>
+      </c>
       <c r="B163" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C163" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D163" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E163" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F163" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G163" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H163" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I163" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J163" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K163" s="29" t="s">
-        <v>181</v>
+        <v>10</v>
+      </c>
+      <c r="C163" s="14">
+        <v>8528</v>
+      </c>
+      <c r="D163" s="15">
+        <v>82</v>
+      </c>
+      <c r="E163" s="15">
+        <v>9</v>
+      </c>
+      <c r="F163" s="15">
+        <v>695</v>
+      </c>
+      <c r="G163" s="15">
+        <v>327</v>
+      </c>
+      <c r="H163" s="15">
+        <v>306</v>
+      </c>
+      <c r="I163" s="15">
+        <v>408</v>
+      </c>
+      <c r="J163" s="15">
+        <v>418</v>
+      </c>
+      <c r="K163" s="15">
+        <v>47</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C164" s="14">
-        <v>8528</v>
+        <v>8353</v>
       </c>
       <c r="D164" s="15">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E164" s="15">
         <v>9</v>
       </c>
       <c r="F164" s="15">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="G164" s="15">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="H164" s="15">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I164" s="15">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="J164" s="15">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="K164" s="15">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B165" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C165" s="14">
-        <v>8353</v>
+        <v>8520</v>
       </c>
       <c r="D165" s="15">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E165" s="15">
         <v>9</v>
       </c>
       <c r="F165" s="15">
-        <v>681</v>
+        <v>695</v>
       </c>
       <c r="G165" s="15">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="H165" s="15">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="I165" s="15">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="J165" s="15">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="K165" s="15">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B166" s="11" t="s">
-        <v>12</v>
+        <v>166</v>
       </c>
       <c r="C166" s="14">
-        <v>8520</v>
+        <v>8995</v>
       </c>
       <c r="D166" s="15">
         <v>82</v>
@@ -5502,135 +5439,135 @@
         <v>9</v>
       </c>
       <c r="F166" s="15">
-        <v>695</v>
+        <v>733</v>
       </c>
       <c r="G166" s="15">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="H166" s="15">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I166" s="15">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J166" s="15">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="K166" s="15">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B167" s="11" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="C167" s="14">
-        <v>8995</v>
+        <v>9408</v>
       </c>
       <c r="D167" s="15">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E167" s="15">
         <v>9</v>
       </c>
       <c r="F167" s="15">
-        <v>733</v>
+        <v>767</v>
       </c>
       <c r="G167" s="15">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="H167" s="15">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="I167" s="15">
-        <v>409</v>
+        <v>350</v>
       </c>
       <c r="J167" s="15">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="K167" s="15">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C168" s="14">
-        <v>9408</v>
+        <v>9003</v>
       </c>
       <c r="D168" s="15">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E168" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F168" s="15">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="G168" s="15">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="H168" s="15">
-        <v>291</v>
+        <v>323</v>
       </c>
       <c r="I168" s="15">
-        <v>350</v>
+        <v>431</v>
       </c>
       <c r="J168" s="15">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="K168" s="15">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B169" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C169" s="14">
-        <v>9003</v>
+        <v>9408</v>
       </c>
       <c r="D169" s="15">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="E169" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F169" s="15">
-        <v>734</v>
+        <v>767</v>
       </c>
       <c r="G169" s="15">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="H169" s="15">
-        <v>323</v>
+        <v>291</v>
       </c>
       <c r="I169" s="15">
-        <v>431</v>
+        <v>350</v>
       </c>
       <c r="J169" s="15">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="K169" s="15">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" s="13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B170" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C170" s="14">
         <v>9408</v>
@@ -5662,118 +5599,118 @@
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" s="13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B171" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C171" s="14">
-        <v>9408</v>
+        <v>8771</v>
       </c>
       <c r="D171" s="15">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E171" s="15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F171" s="15">
-        <v>767</v>
+        <v>715</v>
       </c>
       <c r="G171" s="15">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="H171" s="15">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="I171" s="15">
+        <v>420</v>
+      </c>
+      <c r="J171" s="15">
+        <v>429</v>
+      </c>
+      <c r="K171" s="15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A172" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B172" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C172" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D172" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E172" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F172" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G172" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H172" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I172" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J172" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K172" s="21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A173" s="13">
+        <v>10</v>
+      </c>
+      <c r="B173" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C173" s="14">
+        <v>8529</v>
+      </c>
+      <c r="D173" s="15">
+        <v>63</v>
+      </c>
+      <c r="E173" s="15">
+        <v>9</v>
+      </c>
+      <c r="F173" s="15">
+        <v>695</v>
+      </c>
+      <c r="G173" s="15">
+        <v>327</v>
+      </c>
+      <c r="H173" s="15">
+        <v>264</v>
+      </c>
+      <c r="I173" s="15">
         <v>350</v>
       </c>
-      <c r="J171" s="15">
-        <v>461</v>
-      </c>
-      <c r="K171" s="15">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A172" s="13">
-        <v>9</v>
-      </c>
-      <c r="B172" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C172" s="14">
-        <v>8771</v>
-      </c>
-      <c r="D172" s="15">
-        <v>84</v>
-      </c>
-      <c r="E172" s="15">
-        <v>13</v>
-      </c>
-      <c r="F172" s="15">
-        <v>715</v>
-      </c>
-      <c r="G172" s="15">
-        <v>336</v>
-      </c>
-      <c r="H172" s="15">
-        <v>315</v>
-      </c>
-      <c r="I172" s="15">
-        <v>420</v>
-      </c>
-      <c r="J172" s="15">
-        <v>429</v>
-      </c>
-      <c r="K172" s="15">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A173" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="B173" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="C173" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D173" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E173" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F173" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G173" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H173" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I173" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J173" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K173" s="29" t="s">
-        <v>181</v>
+      <c r="J173" s="15">
+        <v>418</v>
+      </c>
+      <c r="K173" s="15">
+        <v>46</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B174" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C174" s="14">
-        <v>8529</v>
+        <v>10639</v>
       </c>
       <c r="D174" s="15">
         <v>63</v>
@@ -5782,45 +5719,45 @@
         <v>9</v>
       </c>
       <c r="F174" s="15">
-        <v>695</v>
+        <v>867</v>
       </c>
       <c r="G174" s="15">
-        <v>327</v>
+        <v>797</v>
       </c>
       <c r="H174" s="15">
-        <v>264</v>
+        <v>500</v>
       </c>
       <c r="I174" s="15">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="J174" s="15">
-        <v>418</v>
+        <v>600</v>
       </c>
       <c r="K174" s="15">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" s="13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B175" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C175" s="14">
-        <v>10639</v>
+        <v>8500</v>
       </c>
       <c r="D175" s="15">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="E175" s="15">
-        <v>9</v>
-      </c>
-      <c r="F175" s="15">
-        <v>867</v>
+        <v>15</v>
+      </c>
+      <c r="F175" s="14">
+        <v>1500</v>
       </c>
       <c r="G175" s="15">
-        <v>797</v>
+        <v>500</v>
       </c>
       <c r="H175" s="15">
         <v>500</v>
@@ -5832,88 +5769,88 @@
         <v>600</v>
       </c>
       <c r="K175" s="15">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B176" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C176" s="14">
-        <v>8500</v>
+        <v>9496</v>
       </c>
       <c r="D176" s="15">
         <v>80</v>
       </c>
       <c r="E176" s="15">
-        <v>15</v>
-      </c>
-      <c r="F176" s="14">
-        <v>1500</v>
+        <v>12</v>
+      </c>
+      <c r="F176" s="15">
+        <v>775</v>
       </c>
       <c r="G176" s="15">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="H176" s="15">
-        <v>500</v>
+        <v>391</v>
       </c>
       <c r="I176" s="15">
-        <v>800</v>
+        <v>466</v>
       </c>
       <c r="J176" s="15">
-        <v>600</v>
+        <v>619</v>
       </c>
       <c r="K176" s="15">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B177" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C177" s="14">
-        <v>9496</v>
+        <v>7562</v>
       </c>
       <c r="D177" s="15">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E177" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F177" s="15">
-        <v>775</v>
+        <v>616</v>
       </c>
       <c r="G177" s="15">
-        <v>450</v>
+        <v>290</v>
       </c>
       <c r="H177" s="15">
-        <v>391</v>
+        <v>250</v>
       </c>
       <c r="I177" s="15">
-        <v>466</v>
+        <v>350</v>
       </c>
       <c r="J177" s="15">
-        <v>619</v>
+        <v>370</v>
       </c>
       <c r="K177" s="15">
-        <v>69</v>
+        <v>41</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" s="13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C178" s="14">
-        <v>7562</v>
+        <v>8441</v>
       </c>
       <c r="D178" s="15">
         <v>63</v>
@@ -5922,33 +5859,33 @@
         <v>9</v>
       </c>
       <c r="F178" s="15">
-        <v>616</v>
+        <v>688</v>
       </c>
       <c r="G178" s="15">
-        <v>290</v>
+        <v>324</v>
       </c>
       <c r="H178" s="15">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="I178" s="15">
         <v>350</v>
       </c>
       <c r="J178" s="15">
-        <v>370</v>
+        <v>413</v>
       </c>
       <c r="K178" s="15">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" s="13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B179" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C179" s="14">
-        <v>8441</v>
+        <v>7210</v>
       </c>
       <c r="D179" s="15">
         <v>63</v>
@@ -5957,33 +5894,33 @@
         <v>9</v>
       </c>
       <c r="F179" s="15">
-        <v>688</v>
+        <v>588</v>
       </c>
       <c r="G179" s="15">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="H179" s="15">
-        <v>261</v>
+        <v>223</v>
       </c>
       <c r="I179" s="15">
         <v>350</v>
       </c>
       <c r="J179" s="15">
-        <v>413</v>
+        <v>353</v>
       </c>
       <c r="K179" s="15">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" s="13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B180" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C180" s="14">
-        <v>7210</v>
+        <v>7913</v>
       </c>
       <c r="D180" s="15">
         <v>63</v>
@@ -5992,103 +5929,103 @@
         <v>9</v>
       </c>
       <c r="F180" s="15">
-        <v>588</v>
+        <v>645</v>
       </c>
       <c r="G180" s="15">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="H180" s="15">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="I180" s="15">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="J180" s="15">
-        <v>353</v>
+        <v>387</v>
       </c>
       <c r="K180" s="15">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A181" s="13">
-        <v>17</v>
+      <c r="A181" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="B181" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C181" s="14">
-        <v>7913</v>
-      </c>
-      <c r="D181" s="15">
-        <v>63</v>
-      </c>
-      <c r="E181" s="15">
-        <v>9</v>
-      </c>
-      <c r="F181" s="15">
-        <v>645</v>
-      </c>
-      <c r="G181" s="15">
-        <v>303</v>
-      </c>
-      <c r="H181" s="15">
-        <v>245</v>
-      </c>
-      <c r="I181" s="15">
-        <v>384</v>
-      </c>
-      <c r="J181" s="15">
-        <v>387</v>
-      </c>
-      <c r="K181" s="15">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="C181" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D181" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E181" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F181" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G181" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H181" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I181" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J181" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K181" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A182" s="9" t="s">
-        <v>181</v>
+      <c r="A182" s="13">
+        <v>18</v>
       </c>
       <c r="B182" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C182" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D182" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E182" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F182" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G182" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H182" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I182" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J182" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K182" s="29" t="s">
-        <v>181</v>
+        <v>30</v>
+      </c>
+      <c r="C182" s="14">
+        <v>8001</v>
+      </c>
+      <c r="D182" s="15">
+        <v>72</v>
+      </c>
+      <c r="E182" s="15">
+        <v>9</v>
+      </c>
+      <c r="F182" s="15">
+        <v>652</v>
+      </c>
+      <c r="G182" s="15">
+        <v>307</v>
+      </c>
+      <c r="H182" s="15">
+        <v>275</v>
+      </c>
+      <c r="I182" s="15">
+        <v>392</v>
+      </c>
+      <c r="J182" s="15">
+        <v>392</v>
+      </c>
+      <c r="K182" s="15">
+        <v>44</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B183" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C183" s="14">
-        <v>8001</v>
+        <v>7825</v>
       </c>
       <c r="D183" s="15">
         <v>72</v>
@@ -6097,33 +6034,33 @@
         <v>9</v>
       </c>
       <c r="F183" s="15">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="G183" s="15">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="H183" s="15">
         <v>275</v>
       </c>
       <c r="I183" s="15">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="J183" s="15">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="K183" s="15">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" s="13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B184" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C184" s="14">
-        <v>7825</v>
+        <v>7500</v>
       </c>
       <c r="D184" s="15">
         <v>72</v>
@@ -6132,170 +6069,170 @@
         <v>9</v>
       </c>
       <c r="F184" s="15">
-        <v>638</v>
+        <v>609</v>
       </c>
       <c r="G184" s="15">
+        <v>287</v>
+      </c>
+      <c r="H184" s="15">
+        <v>232</v>
+      </c>
+      <c r="I184" s="15">
+        <v>350</v>
+      </c>
+      <c r="J184" s="15">
+        <v>366</v>
+      </c>
+      <c r="K184" s="15">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A185" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B185" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C185" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D185" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E185" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F185" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G185" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H185" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I185" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J185" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K185" s="21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A186" s="13">
+        <v>21</v>
+      </c>
+      <c r="B186" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C186" s="14">
+        <v>13692</v>
+      </c>
+      <c r="D186" s="15">
+        <v>80</v>
+      </c>
+      <c r="E186" s="15">
+        <v>9</v>
+      </c>
+      <c r="F186" s="15">
+        <v>760</v>
+      </c>
+      <c r="G186" s="15">
+        <v>708</v>
+      </c>
+      <c r="H186" s="15">
         <v>300</v>
       </c>
-      <c r="H184" s="15">
-        <v>275</v>
-      </c>
-      <c r="I184" s="15">
-        <v>383</v>
-      </c>
-      <c r="J184" s="15">
-        <v>383</v>
-      </c>
-      <c r="K184" s="15">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A185" s="13">
-        <v>20</v>
-      </c>
-      <c r="B185" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C185" s="14">
-        <v>7500</v>
-      </c>
-      <c r="D185" s="15">
-        <v>72</v>
-      </c>
-      <c r="E185" s="15">
-        <v>9</v>
-      </c>
-      <c r="F185" s="15">
-        <v>609</v>
-      </c>
-      <c r="G185" s="15">
-        <v>287</v>
-      </c>
-      <c r="H185" s="15">
-        <v>232</v>
-      </c>
-      <c r="I185" s="15">
-        <v>350</v>
-      </c>
-      <c r="J185" s="15">
-        <v>366</v>
-      </c>
-      <c r="K185" s="15">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A186" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="B186" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C186" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D186" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E186" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F186" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G186" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H186" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I186" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J186" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K186" s="29" t="s">
-        <v>181</v>
+      <c r="I186" s="15">
+        <v>608</v>
+      </c>
+      <c r="J186" s="15">
+        <v>821</v>
+      </c>
+      <c r="K186" s="15">
+        <v>51</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" s="13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B187" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C187" s="14">
-        <v>13692</v>
+        <v>13434</v>
       </c>
       <c r="D187" s="15">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E187" s="15">
         <v>9</v>
       </c>
       <c r="F187" s="15">
-        <v>760</v>
+        <v>745</v>
       </c>
       <c r="G187" s="15">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="H187" s="15">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="I187" s="15">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="J187" s="15">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="K187" s="15">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C188" s="14">
-        <v>13434</v>
+        <v>13951</v>
       </c>
       <c r="D188" s="15">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E188" s="15">
         <v>9</v>
       </c>
       <c r="F188" s="15">
-        <v>745</v>
+        <v>774</v>
       </c>
       <c r="G188" s="15">
-        <v>695</v>
+        <v>722</v>
       </c>
       <c r="H188" s="15">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="I188" s="15">
-        <v>596</v>
+        <v>619</v>
       </c>
       <c r="J188" s="15">
-        <v>806</v>
+        <v>837</v>
       </c>
       <c r="K188" s="15">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A189" s="13">
-        <v>23</v>
+      <c r="A189" s="16">
+        <v>24</v>
       </c>
       <c r="B189" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C189" s="14">
         <v>13951</v>
@@ -6326,140 +6263,140 @@
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A190" s="16">
-        <v>24</v>
+      <c r="A190" s="13">
+        <v>25</v>
       </c>
       <c r="B190" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C190" s="14">
-        <v>13951</v>
+        <v>13176</v>
       </c>
       <c r="D190" s="15">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E190" s="15">
         <v>9</v>
       </c>
       <c r="F190" s="15">
-        <v>774</v>
+        <v>731</v>
       </c>
       <c r="G190" s="15">
-        <v>722</v>
+        <v>682</v>
       </c>
       <c r="H190" s="15">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="I190" s="15">
-        <v>619</v>
+        <v>585</v>
       </c>
       <c r="J190" s="15">
-        <v>837</v>
+        <v>790</v>
       </c>
       <c r="K190" s="15">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" s="13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B191" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C191" s="14">
-        <v>13176</v>
+        <v>24268</v>
       </c>
       <c r="D191" s="15">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E191" s="15">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F191" s="15">
-        <v>731</v>
+        <v>960</v>
       </c>
       <c r="G191" s="15">
-        <v>682</v>
+        <v>895</v>
       </c>
       <c r="H191" s="15">
-        <v>287</v>
-      </c>
-      <c r="I191" s="15">
-        <v>585</v>
-      </c>
-      <c r="J191" s="15">
-        <v>790</v>
+        <v>431</v>
+      </c>
+      <c r="I191" s="19">
+        <v>1.1359999999999999</v>
+      </c>
+      <c r="J191" s="14">
+        <v>1308</v>
       </c>
       <c r="K191" s="15">
-        <v>49</v>
+        <v>99</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" s="13">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B192" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C192" s="14">
-        <v>24268</v>
+        <v>13176</v>
       </c>
       <c r="D192" s="15">
         <v>80</v>
       </c>
       <c r="E192" s="15">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F192" s="15">
-        <v>960</v>
+        <v>731</v>
       </c>
       <c r="G192" s="15">
-        <v>895</v>
+        <v>682</v>
       </c>
       <c r="H192" s="15">
-        <v>431</v>
-      </c>
-      <c r="I192" s="27">
-        <v>1.1359999999999999</v>
-      </c>
-      <c r="J192" s="14">
-        <v>1308</v>
+        <v>287</v>
+      </c>
+      <c r="I192" s="15">
+        <v>585</v>
+      </c>
+      <c r="J192" s="15">
+        <v>790</v>
       </c>
       <c r="K192" s="15">
-        <v>99</v>
+        <v>49</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" s="13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B193" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C193" s="14">
-        <v>13176</v>
+        <v>13308</v>
       </c>
       <c r="D193" s="15">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E193" s="15">
         <v>9</v>
       </c>
       <c r="F193" s="15">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="G193" s="15">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="H193" s="15">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="I193" s="15">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="J193" s="15">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="K193" s="15">
         <v>49</v>
@@ -6467,80 +6404,80 @@
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" s="13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B194" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C194" s="14">
-        <v>13308</v>
+        <v>17309</v>
       </c>
       <c r="D194" s="15">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E194" s="15">
         <v>9</v>
       </c>
       <c r="F194" s="15">
-        <v>738</v>
+        <v>960</v>
       </c>
       <c r="G194" s="15">
-        <v>689</v>
+        <v>895</v>
       </c>
       <c r="H194" s="15">
-        <v>290</v>
+        <v>377</v>
       </c>
       <c r="I194" s="15">
-        <v>591</v>
-      </c>
-      <c r="J194" s="15">
-        <v>798</v>
+        <v>768</v>
+      </c>
+      <c r="J194" s="14">
+        <v>1308</v>
       </c>
       <c r="K194" s="15">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" s="13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B195" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C195" s="14">
-        <v>17309</v>
+        <v>13176</v>
       </c>
       <c r="D195" s="15">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E195" s="15">
         <v>9</v>
       </c>
       <c r="F195" s="15">
-        <v>960</v>
+        <v>731</v>
       </c>
       <c r="G195" s="15">
-        <v>895</v>
+        <v>682</v>
       </c>
       <c r="H195" s="15">
-        <v>377</v>
+        <v>287</v>
       </c>
       <c r="I195" s="15">
-        <v>768</v>
-      </c>
-      <c r="J195" s="14">
-        <v>1308</v>
+        <v>585</v>
+      </c>
+      <c r="J195" s="15">
+        <v>790</v>
       </c>
       <c r="K195" s="15">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" s="13">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C196" s="14">
         <v>13176</v>
@@ -6572,10 +6509,10 @@
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" s="13">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B197" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C197" s="14">
         <v>13176</v>
@@ -6606,154 +6543,154 @@
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A198" s="13">
-        <v>32</v>
+      <c r="A198" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="B198" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C198" s="14">
-        <v>13176</v>
-      </c>
-      <c r="D198" s="15">
-        <v>72</v>
-      </c>
-      <c r="E198" s="15">
-        <v>9</v>
-      </c>
-      <c r="F198" s="15">
-        <v>731</v>
-      </c>
-      <c r="G198" s="15">
-        <v>682</v>
-      </c>
-      <c r="H198" s="15">
-        <v>287</v>
-      </c>
-      <c r="I198" s="15">
-        <v>585</v>
-      </c>
-      <c r="J198" s="15">
-        <v>790</v>
-      </c>
-      <c r="K198" s="15">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="C198" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D198" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E198" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F198" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G198" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H198" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I198" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J198" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K198" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A199" s="9" t="s">
-        <v>181</v>
+      <c r="A199" s="13">
+        <v>33</v>
       </c>
       <c r="B199" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C199" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D199" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E199" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F199" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G199" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H199" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I199" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J199" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K199" s="29" t="s">
-        <v>181</v>
+        <v>168</v>
+      </c>
+      <c r="C199" s="14">
+        <v>14597</v>
+      </c>
+      <c r="D199" s="15">
+        <v>80</v>
+      </c>
+      <c r="E199" s="15">
+        <v>9</v>
+      </c>
+      <c r="F199" s="15">
+        <v>810</v>
+      </c>
+      <c r="G199" s="15">
+        <v>755</v>
+      </c>
+      <c r="H199" s="15">
+        <v>318</v>
+      </c>
+      <c r="I199" s="15">
+        <v>648</v>
+      </c>
+      <c r="J199" s="15">
+        <v>876</v>
+      </c>
+      <c r="K199" s="15">
+        <v>54</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="13">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B200" s="11" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C200" s="14">
-        <v>14597</v>
+        <v>13434</v>
       </c>
       <c r="D200" s="15">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E200" s="15">
         <v>9</v>
       </c>
       <c r="F200" s="15">
-        <v>810</v>
+        <v>745</v>
       </c>
       <c r="G200" s="15">
-        <v>755</v>
+        <v>695</v>
       </c>
       <c r="H200" s="15">
-        <v>318</v>
+        <v>293</v>
       </c>
       <c r="I200" s="15">
-        <v>648</v>
+        <v>596</v>
       </c>
       <c r="J200" s="15">
-        <v>876</v>
+        <v>806</v>
       </c>
       <c r="K200" s="15">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" s="13">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B201" s="11" t="s">
-        <v>177</v>
+        <v>49</v>
       </c>
       <c r="C201" s="14">
-        <v>13434</v>
+        <v>13176</v>
       </c>
       <c r="D201" s="15">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E201" s="15">
         <v>9</v>
       </c>
       <c r="F201" s="15">
-        <v>745</v>
+        <v>731</v>
       </c>
       <c r="G201" s="15">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="H201" s="15">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="I201" s="15">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="J201" s="15">
-        <v>806</v>
+        <v>791</v>
       </c>
       <c r="K201" s="15">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" s="13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B202" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C202" s="14">
-        <v>13176</v>
+        <v>13563</v>
       </c>
       <c r="D202" s="15">
         <v>80</v>
@@ -6762,33 +6699,33 @@
         <v>9</v>
       </c>
       <c r="F202" s="15">
-        <v>731</v>
+        <v>753</v>
       </c>
       <c r="G202" s="15">
-        <v>682</v>
+        <v>702</v>
       </c>
       <c r="H202" s="15">
         <v>300</v>
       </c>
       <c r="I202" s="15">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="J202" s="15">
-        <v>791</v>
+        <v>814</v>
       </c>
       <c r="K202" s="15">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" s="13">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B203" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C203" s="14">
-        <v>13563</v>
+        <v>16147</v>
       </c>
       <c r="D203" s="15">
         <v>80</v>
@@ -6797,103 +6734,103 @@
         <v>9</v>
       </c>
       <c r="F203" s="15">
-        <v>753</v>
+        <v>896</v>
       </c>
       <c r="G203" s="15">
-        <v>702</v>
+        <v>835</v>
       </c>
       <c r="H203" s="15">
-        <v>300</v>
+        <v>352</v>
       </c>
       <c r="I203" s="15">
-        <v>602</v>
+        <v>717</v>
       </c>
       <c r="J203" s="15">
-        <v>814</v>
+        <v>969</v>
       </c>
       <c r="K203" s="15">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A204" s="13">
-        <v>37</v>
+      <c r="A204" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="B204" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C204" s="14">
-        <v>16147</v>
-      </c>
-      <c r="D204" s="15">
-        <v>80</v>
-      </c>
-      <c r="E204" s="15">
-        <v>9</v>
-      </c>
-      <c r="F204" s="15">
-        <v>896</v>
-      </c>
-      <c r="G204" s="15">
-        <v>835</v>
-      </c>
-      <c r="H204" s="15">
-        <v>352</v>
-      </c>
-      <c r="I204" s="15">
-        <v>717</v>
-      </c>
-      <c r="J204" s="15">
-        <v>969</v>
-      </c>
-      <c r="K204" s="15">
-        <v>60</v>
+        <v>52</v>
+      </c>
+      <c r="C204" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D204" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E204" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F204" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G204" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H204" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I204" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J204" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K204" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A205" s="9" t="s">
-        <v>181</v>
+      <c r="A205" s="13">
+        <v>38</v>
       </c>
       <c r="B205" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C205" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D205" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E205" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F205" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G205" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H205" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I205" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J205" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K205" s="29" t="s">
-        <v>181</v>
+        <v>53</v>
+      </c>
+      <c r="C205" s="14">
+        <v>11109</v>
+      </c>
+      <c r="D205" s="15">
+        <v>72</v>
+      </c>
+      <c r="E205" s="15">
+        <v>9</v>
+      </c>
+      <c r="F205" s="15">
+        <v>616</v>
+      </c>
+      <c r="G205" s="15">
+        <v>302</v>
+      </c>
+      <c r="H205" s="15">
+        <v>242</v>
+      </c>
+      <c r="I205" s="15">
+        <v>493</v>
+      </c>
+      <c r="J205" s="15">
+        <v>667</v>
+      </c>
+      <c r="K205" s="15">
+        <v>41</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" s="13">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B206" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C206" s="14">
-        <v>11109</v>
+        <v>17730</v>
       </c>
       <c r="D206" s="15">
         <v>72</v>
@@ -6902,33 +6839,33 @@
         <v>9</v>
       </c>
       <c r="F206" s="15">
-        <v>616</v>
+        <v>667</v>
       </c>
       <c r="G206" s="15">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="H206" s="15">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="I206" s="15">
-        <v>493</v>
+        <v>533</v>
       </c>
       <c r="J206" s="15">
-        <v>667</v>
+        <v>721</v>
       </c>
       <c r="K206" s="15">
-        <v>41</v>
+        <v>70</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" s="13">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B207" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C207" s="14">
-        <v>17730</v>
+        <v>12142</v>
       </c>
       <c r="D207" s="15">
         <v>72</v>
@@ -6937,33 +6874,33 @@
         <v>9</v>
       </c>
       <c r="F207" s="15">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="G207" s="15">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="H207" s="15">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="I207" s="15">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="J207" s="15">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="K207" s="15">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" s="13">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B208" s="11" t="s">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="C208" s="14">
-        <v>12142</v>
+        <v>12401</v>
       </c>
       <c r="D208" s="15">
         <v>72</v>
@@ -6972,33 +6909,33 @@
         <v>9</v>
       </c>
       <c r="F208" s="15">
-        <v>674</v>
+        <v>688</v>
       </c>
       <c r="G208" s="15">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="H208" s="15">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="I208" s="15">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="J208" s="15">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="K208" s="15">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" s="13">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B209" s="11" t="s">
-        <v>178</v>
+        <v>57</v>
       </c>
       <c r="C209" s="14">
-        <v>12401</v>
+        <v>12659</v>
       </c>
       <c r="D209" s="15">
         <v>72</v>
@@ -7007,208 +6944,208 @@
         <v>9</v>
       </c>
       <c r="F209" s="15">
-        <v>688</v>
+        <v>702</v>
       </c>
       <c r="G209" s="15">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="H209" s="15">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I209" s="15">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="J209" s="15">
-        <v>744</v>
+        <v>760</v>
       </c>
       <c r="K209" s="15">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" s="13">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B210" s="11" t="s">
-        <v>57</v>
+        <v>171</v>
       </c>
       <c r="C210" s="14">
-        <v>12659</v>
+        <v>14500</v>
       </c>
       <c r="D210" s="15">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="E210" s="15">
-        <v>9</v>
-      </c>
-      <c r="F210" s="15">
-        <v>702</v>
+        <v>20</v>
+      </c>
+      <c r="F210" s="14">
+        <v>1500</v>
       </c>
       <c r="G210" s="15">
-        <v>344</v>
+        <v>500</v>
       </c>
       <c r="H210" s="15">
-        <v>276</v>
+        <v>400</v>
       </c>
       <c r="I210" s="15">
-        <v>562</v>
+        <v>750</v>
       </c>
       <c r="J210" s="15">
-        <v>760</v>
+        <v>950</v>
       </c>
       <c r="K210" s="15">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211" s="13">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B211" s="11" t="s">
-        <v>179</v>
+        <v>59</v>
       </c>
       <c r="C211" s="14">
-        <v>14500</v>
+        <v>12091</v>
       </c>
       <c r="D211" s="15">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E211" s="15">
-        <v>20</v>
-      </c>
-      <c r="F211" s="14">
-        <v>1500</v>
+        <v>9</v>
+      </c>
+      <c r="F211" s="15">
+        <v>671</v>
       </c>
       <c r="G211" s="15">
-        <v>500</v>
+        <v>329</v>
       </c>
       <c r="H211" s="15">
-        <v>400</v>
+        <v>286</v>
       </c>
       <c r="I211" s="15">
-        <v>750</v>
+        <v>537</v>
       </c>
       <c r="J211" s="15">
-        <v>950</v>
+        <v>726</v>
       </c>
       <c r="K211" s="15">
-        <v>75</v>
+        <v>45</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212" s="13">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B212" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C212" s="14">
-        <v>12091</v>
+        <v>13563</v>
       </c>
       <c r="D212" s="15">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E212" s="15">
         <v>9</v>
       </c>
       <c r="F212" s="15">
-        <v>671</v>
+        <v>753</v>
       </c>
       <c r="G212" s="15">
-        <v>329</v>
+        <v>368</v>
       </c>
       <c r="H212" s="15">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="I212" s="15">
-        <v>537</v>
+        <v>602</v>
       </c>
       <c r="J212" s="15">
-        <v>726</v>
+        <v>814</v>
       </c>
       <c r="K212" s="15">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A213" s="13">
-        <v>45</v>
+      <c r="A213" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="B213" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C213" s="14">
-        <v>13563</v>
-      </c>
-      <c r="D213" s="15">
+        <v>61</v>
+      </c>
+      <c r="C213" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D213" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E213" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F213" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G213" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H213" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I213" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J213" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K213" s="21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A214" s="13">
+        <v>46</v>
+      </c>
+      <c r="B214" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C214" s="14">
+        <v>13176</v>
+      </c>
+      <c r="D214" s="15">
         <v>72</v>
       </c>
-      <c r="E213" s="15">
-        <v>9</v>
-      </c>
-      <c r="F213" s="15">
-        <v>753</v>
-      </c>
-      <c r="G213" s="15">
-        <v>368</v>
-      </c>
-      <c r="H213" s="15">
-        <v>295</v>
-      </c>
-      <c r="I213" s="15">
-        <v>602</v>
-      </c>
-      <c r="J213" s="15">
-        <v>814</v>
-      </c>
-      <c r="K213" s="15">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A214" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="B214" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C214" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D214" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E214" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F214" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G214" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H214" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I214" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J214" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K214" s="29" t="s">
-        <v>181</v>
+      <c r="E214" s="15">
+        <v>9</v>
+      </c>
+      <c r="F214" s="15">
+        <v>731</v>
+      </c>
+      <c r="G214" s="15">
+        <v>358</v>
+      </c>
+      <c r="H214" s="15">
+        <v>287</v>
+      </c>
+      <c r="I214" s="15">
+        <v>585</v>
+      </c>
+      <c r="J214" s="15">
+        <v>791</v>
+      </c>
+      <c r="K214" s="15">
+        <v>49</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215" s="13">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B215" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C215" s="14">
-        <v>13176</v>
+        <v>11496</v>
       </c>
       <c r="D215" s="15">
         <v>72</v>
@@ -7217,33 +7154,33 @@
         <v>9</v>
       </c>
       <c r="F215" s="15">
-        <v>731</v>
+        <v>638</v>
       </c>
       <c r="G215" s="15">
-        <v>358</v>
+        <v>312</v>
       </c>
       <c r="H215" s="15">
-        <v>287</v>
+        <v>250</v>
       </c>
       <c r="I215" s="15">
-        <v>585</v>
+        <v>510</v>
       </c>
       <c r="J215" s="15">
-        <v>791</v>
+        <v>690</v>
       </c>
       <c r="K215" s="15">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A216" s="13">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B216" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C216" s="14">
-        <v>11496</v>
+        <v>12981</v>
       </c>
       <c r="D216" s="15">
         <v>72</v>
@@ -7252,33 +7189,33 @@
         <v>9</v>
       </c>
       <c r="F216" s="15">
-        <v>638</v>
+        <v>721</v>
       </c>
       <c r="G216" s="15">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="H216" s="15">
-        <v>250</v>
+        <v>314</v>
       </c>
       <c r="I216" s="15">
-        <v>510</v>
+        <v>577</v>
       </c>
       <c r="J216" s="15">
-        <v>690</v>
+        <v>779</v>
       </c>
       <c r="K216" s="15">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" s="13">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B217" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C217" s="14">
-        <v>12981</v>
+        <v>14000</v>
       </c>
       <c r="D217" s="15">
         <v>72</v>
@@ -7287,33 +7224,33 @@
         <v>9</v>
       </c>
       <c r="F217" s="15">
-        <v>721</v>
+        <v>781</v>
       </c>
       <c r="G217" s="15">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="H217" s="15">
-        <v>314</v>
+        <v>472</v>
       </c>
       <c r="I217" s="15">
-        <v>577</v>
+        <v>654</v>
       </c>
       <c r="J217" s="15">
-        <v>779</v>
+        <v>845</v>
       </c>
       <c r="K217" s="15">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" s="13">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B218" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C218" s="14">
-        <v>14000</v>
+        <v>11367</v>
       </c>
       <c r="D218" s="15">
         <v>72</v>
@@ -7322,30 +7259,30 @@
         <v>9</v>
       </c>
       <c r="F218" s="15">
-        <v>781</v>
+        <v>631</v>
       </c>
       <c r="G218" s="15">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="H218" s="15">
-        <v>472</v>
+        <v>275</v>
       </c>
       <c r="I218" s="15">
-        <v>654</v>
+        <v>505</v>
       </c>
       <c r="J218" s="15">
-        <v>845</v>
+        <v>682</v>
       </c>
       <c r="K218" s="15">
-        <v>57</v>
+        <v>42</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219" s="13">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B219" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C219" s="14">
         <v>11367</v>
@@ -7377,10 +7314,10 @@
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" s="13">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B220" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C220" s="14">
         <v>11367</v>
@@ -7398,27 +7335,27 @@
         <v>309</v>
       </c>
       <c r="H220" s="15">
-        <v>275</v>
+        <v>596</v>
       </c>
       <c r="I220" s="15">
-        <v>505</v>
+        <v>800</v>
       </c>
       <c r="J220" s="15">
         <v>682</v>
       </c>
       <c r="K220" s="15">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221" s="13">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B221" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C221" s="14">
-        <v>11367</v>
+        <v>12401</v>
       </c>
       <c r="D221" s="15">
         <v>72</v>
@@ -7427,103 +7364,103 @@
         <v>9</v>
       </c>
       <c r="F221" s="15">
-        <v>631</v>
+        <v>688</v>
       </c>
       <c r="G221" s="15">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="H221" s="15">
+        <v>387</v>
+      </c>
+      <c r="I221" s="15">
         <v>596</v>
       </c>
-      <c r="I221" s="15">
-        <v>800</v>
-      </c>
       <c r="J221" s="15">
-        <v>682</v>
+        <v>744</v>
       </c>
       <c r="K221" s="15">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A222" s="13">
-        <v>53</v>
+      <c r="A222" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="B222" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C222" s="14">
-        <v>12401</v>
-      </c>
-      <c r="D222" s="15">
+        <v>70</v>
+      </c>
+      <c r="C222" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D222" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E222" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F222" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G222" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H222" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I222" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J222" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K222" s="21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A223" s="13">
+        <v>54</v>
+      </c>
+      <c r="B223" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C223" s="14">
+        <v>12479</v>
+      </c>
+      <c r="D223" s="15">
         <v>72</v>
       </c>
-      <c r="E222" s="15">
-        <v>9</v>
-      </c>
-      <c r="F222" s="15">
-        <v>688</v>
-      </c>
-      <c r="G222" s="15">
-        <v>337</v>
-      </c>
-      <c r="H222" s="15">
-        <v>387</v>
-      </c>
-      <c r="I222" s="15">
-        <v>596</v>
-      </c>
-      <c r="J222" s="15">
-        <v>744</v>
-      </c>
-      <c r="K222" s="15">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A223" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="B223" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C223" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D223" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E223" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F223" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G223" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H223" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I223" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J223" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K223" s="29" t="s">
-        <v>181</v>
+      <c r="E223" s="15">
+        <v>9</v>
+      </c>
+      <c r="F223" s="15">
+        <v>353</v>
+      </c>
+      <c r="G223" s="15">
+        <v>204</v>
+      </c>
+      <c r="H223" s="15">
+        <v>275</v>
+      </c>
+      <c r="I223" s="15">
+        <v>663</v>
+      </c>
+      <c r="J223" s="15">
+        <v>153</v>
+      </c>
+      <c r="K223" s="15">
+        <v>43</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224" s="13">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B224" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C224" s="14">
-        <v>12479</v>
+        <v>12234</v>
       </c>
       <c r="D224" s="15">
         <v>72</v>
@@ -7532,30 +7469,30 @@
         <v>9</v>
       </c>
       <c r="F224" s="15">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="G224" s="15">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H224" s="15">
         <v>275</v>
       </c>
       <c r="I224" s="15">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="J224" s="15">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="K224" s="15">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225" s="13">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B225" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C225" s="14">
         <v>12234</v>
@@ -7586,87 +7523,87 @@
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A226" s="13">
-        <v>56</v>
+      <c r="A226" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="B226" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C226" s="14">
-        <v>12234</v>
-      </c>
-      <c r="D226" s="15">
+        <v>74</v>
+      </c>
+      <c r="C226" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D226" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E226" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F226" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G226" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H226" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I226" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J226" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K226" s="21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A227" s="13">
+        <v>57</v>
+      </c>
+      <c r="B227" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C227" s="14">
+        <v>11133</v>
+      </c>
+      <c r="D227" s="15">
         <v>72</v>
       </c>
-      <c r="E226" s="15">
-        <v>9</v>
-      </c>
-      <c r="F226" s="15">
-        <v>349</v>
-      </c>
-      <c r="G226" s="15">
-        <v>200</v>
-      </c>
-      <c r="H226" s="15">
+      <c r="E227" s="15">
+        <v>9</v>
+      </c>
+      <c r="F227" s="15">
+        <v>315</v>
+      </c>
+      <c r="G227" s="15">
+        <v>259</v>
+      </c>
+      <c r="H227" s="15">
         <v>275</v>
       </c>
-      <c r="I226" s="15">
-        <v>650</v>
-      </c>
-      <c r="J226" s="15">
-        <v>150</v>
-      </c>
-      <c r="K226" s="15">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A227" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="B227" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C227" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D227" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E227" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F227" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G227" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H227" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I227" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J227" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K227" s="29" t="s">
-        <v>181</v>
+      <c r="I227" s="15">
+        <v>710</v>
+      </c>
+      <c r="J227" s="15">
+        <v>710</v>
+      </c>
+      <c r="K227" s="15">
+        <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228" s="13">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B228" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C228" s="14">
-        <v>11133</v>
+        <v>13756</v>
       </c>
       <c r="D228" s="15">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E228" s="15">
         <v>9</v>
@@ -7675,16 +7612,16 @@
         <v>315</v>
       </c>
       <c r="G228" s="15">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="H228" s="15">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="I228" s="15">
-        <v>710</v>
+        <v>663</v>
       </c>
       <c r="J228" s="15">
-        <v>710</v>
+        <v>663</v>
       </c>
       <c r="K228" s="15">
         <v>8</v>
@@ -7692,16 +7629,16 @@
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229" s="13">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B229" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C229" s="14">
-        <v>13756</v>
+        <v>11133</v>
       </c>
       <c r="D229" s="15">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E229" s="15">
         <v>9</v>
@@ -7710,16 +7647,16 @@
         <v>315</v>
       </c>
       <c r="G229" s="15">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="H229" s="15">
         <v>250</v>
       </c>
       <c r="I229" s="15">
-        <v>663</v>
+        <v>710</v>
       </c>
       <c r="J229" s="15">
-        <v>663</v>
+        <v>710</v>
       </c>
       <c r="K229" s="15">
         <v>8</v>
@@ -7727,34 +7664,34 @@
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230" s="13">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B230" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C230" s="14">
-        <v>11133</v>
+        <v>10766</v>
       </c>
       <c r="D230" s="15">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E230" s="15">
         <v>9</v>
       </c>
       <c r="F230" s="15">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="G230" s="15">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="H230" s="15">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="I230" s="15">
-        <v>710</v>
+        <v>686</v>
       </c>
       <c r="J230" s="15">
-        <v>710</v>
+        <v>686</v>
       </c>
       <c r="K230" s="15">
         <v>8</v>
@@ -7762,398 +7699,398 @@
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A231" s="13">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B231" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C231" s="14">
-        <v>10766</v>
+        <v>11500</v>
       </c>
       <c r="D231" s="15">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E231" s="15">
         <v>9</v>
       </c>
       <c r="F231" s="15">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="G231" s="15">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="H231" s="15">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="I231" s="15">
-        <v>686</v>
+        <v>733</v>
       </c>
       <c r="J231" s="15">
-        <v>686</v>
+        <v>733</v>
       </c>
       <c r="K231" s="15">
         <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A232" s="13">
-        <v>61</v>
+      <c r="A232" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="B232" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C232" s="14">
-        <v>11500</v>
-      </c>
-      <c r="D232" s="15">
-        <v>63</v>
-      </c>
-      <c r="E232" s="15">
-        <v>9</v>
-      </c>
-      <c r="F232" s="15">
-        <v>325</v>
-      </c>
-      <c r="G232" s="15">
-        <v>268</v>
-      </c>
-      <c r="H232" s="15">
-        <v>250</v>
-      </c>
-      <c r="I232" s="15">
-        <v>733</v>
-      </c>
-      <c r="J232" s="15">
-        <v>733</v>
-      </c>
-      <c r="K232" s="15">
+        <v>80</v>
+      </c>
+      <c r="C232" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D232" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E232" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F232" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G232" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H232" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I232" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J232" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K232" s="21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A233" s="13">
+        <v>62</v>
+      </c>
+      <c r="B233" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C233" s="14">
+        <v>11745</v>
+      </c>
+      <c r="D233" s="15">
+        <v>76</v>
+      </c>
+      <c r="E233" s="15">
+        <v>9</v>
+      </c>
+      <c r="F233" s="15">
+        <v>332</v>
+      </c>
+      <c r="G233" s="15">
+        <v>273</v>
+      </c>
+      <c r="H233" s="15">
+        <v>475</v>
+      </c>
+      <c r="I233" s="15">
+        <v>350</v>
+      </c>
+      <c r="J233" s="15">
+        <v>844</v>
+      </c>
+      <c r="K233" s="15">
         <v>8</v>
-      </c>
-    </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A233" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="B233" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C233" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D233" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E233" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F233" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G233" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H233" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I233" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J233" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K233" s="29" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A234" s="13">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B234" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C234" s="14">
-        <v>11745</v>
+        <v>13457</v>
       </c>
       <c r="D234" s="15">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E234" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F234" s="15">
-        <v>332</v>
+        <v>608</v>
       </c>
       <c r="G234" s="15">
-        <v>273</v>
+        <v>313</v>
       </c>
       <c r="H234" s="15">
-        <v>475</v>
+        <v>343</v>
       </c>
       <c r="I234" s="15">
         <v>350</v>
       </c>
       <c r="J234" s="15">
-        <v>844</v>
+        <v>857</v>
       </c>
       <c r="K234" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235" s="13">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B235" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C235" s="14">
+        <v>12380</v>
+      </c>
+      <c r="D235" s="15">
         <v>82</v>
-      </c>
-      <c r="C235" s="14">
-        <v>13457</v>
-      </c>
-      <c r="D235" s="15">
-        <v>90</v>
       </c>
       <c r="E235" s="15">
         <v>11</v>
       </c>
       <c r="F235" s="15">
-        <v>608</v>
+        <v>500</v>
       </c>
       <c r="G235" s="15">
-        <v>313</v>
+        <v>350</v>
       </c>
       <c r="H235" s="15">
-        <v>343</v>
+        <v>316</v>
       </c>
       <c r="I235" s="15">
-        <v>350</v>
+        <v>257</v>
       </c>
       <c r="J235" s="15">
-        <v>857</v>
+        <v>788</v>
       </c>
       <c r="K235" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A236" s="13">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B236" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C236" s="14">
-        <v>12380</v>
+        <v>12650</v>
       </c>
       <c r="D236" s="15">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E236" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F236" s="15">
-        <v>500</v>
+        <v>357</v>
       </c>
       <c r="G236" s="15">
-        <v>350</v>
+        <v>295</v>
       </c>
       <c r="H236" s="15">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="I236" s="15">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="J236" s="15">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="K236" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A237" s="13">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B237" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C237" s="14">
-        <v>12650</v>
+        <v>12380</v>
       </c>
       <c r="D237" s="15">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E237" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F237" s="15">
-        <v>357</v>
+        <v>500</v>
       </c>
       <c r="G237" s="15">
-        <v>295</v>
+        <v>350</v>
       </c>
       <c r="H237" s="15">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="I237" s="15">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="J237" s="15">
-        <v>806</v>
+        <v>788</v>
       </c>
       <c r="K237" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A238" s="13">
-        <v>66</v>
+      <c r="A238" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="B238" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C238" s="14">
-        <v>12380</v>
-      </c>
-      <c r="D238" s="15">
-        <v>82</v>
-      </c>
-      <c r="E238" s="15">
-        <v>11</v>
-      </c>
-      <c r="F238" s="15">
-        <v>500</v>
-      </c>
-      <c r="G238" s="15">
+        <v>86</v>
+      </c>
+      <c r="C238" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D238" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E238" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F238" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G238" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H238" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I238" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J238" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K238" s="21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A239" s="13">
+        <v>67</v>
+      </c>
+      <c r="B239" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C239" s="14">
+        <v>10766</v>
+      </c>
+      <c r="D239" s="15">
+        <v>72</v>
+      </c>
+      <c r="E239" s="15">
+        <v>9</v>
+      </c>
+      <c r="F239" s="15">
+        <v>304</v>
+      </c>
+      <c r="G239" s="15">
+        <v>251</v>
+      </c>
+      <c r="H239" s="15">
+        <v>275</v>
+      </c>
+      <c r="I239" s="15">
         <v>350</v>
       </c>
-      <c r="H238" s="15">
-        <v>316</v>
-      </c>
-      <c r="I238" s="15">
-        <v>267</v>
-      </c>
-      <c r="J238" s="15">
-        <v>788</v>
-      </c>
-      <c r="K238" s="15">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A239" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="B239" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C239" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D239" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E239" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F239" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G239" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H239" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I239" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J239" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K239" s="29" t="s">
-        <v>181</v>
+      <c r="J239" s="15">
+        <v>150</v>
+      </c>
+      <c r="K239" s="15">
+        <v>47</v>
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240" s="13">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B240" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C240" s="14">
-        <v>10766</v>
+        <v>12091</v>
       </c>
       <c r="D240" s="15">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E240" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F240" s="15">
-        <v>304</v>
+        <v>342</v>
       </c>
       <c r="G240" s="15">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="H240" s="15">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="I240" s="15">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="J240" s="15">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="K240" s="15">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241" s="13">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B241" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C241" s="14">
-        <v>12091</v>
+        <v>11623</v>
       </c>
       <c r="D241" s="15">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E241" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F241" s="15">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="G241" s="15">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="H241" s="15">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I241" s="15">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="J241" s="15">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="K241" s="15">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A242" s="13">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B242" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C242" s="14">
-        <v>11623</v>
+        <v>10644</v>
       </c>
       <c r="D242" s="15">
         <v>72</v>
@@ -8162,10 +8099,10 @@
         <v>9</v>
       </c>
       <c r="F242" s="15">
-        <v>329</v>
+        <v>301</v>
       </c>
       <c r="G242" s="15">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="H242" s="15">
         <v>275</v>
@@ -8174,21 +8111,21 @@
         <v>350</v>
       </c>
       <c r="J242" s="15">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K242" s="15">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A243" s="13">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B243" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C243" s="14">
-        <v>10644</v>
+        <v>10154</v>
       </c>
       <c r="D243" s="15">
         <v>72</v>
@@ -8197,10 +8134,10 @@
         <v>9</v>
       </c>
       <c r="F243" s="15">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="G243" s="15">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="H243" s="15">
         <v>275</v>
@@ -8212,18 +8149,18 @@
         <v>150</v>
       </c>
       <c r="K243" s="15">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A244" s="13">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B244" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C244" s="14">
-        <v>10154</v>
+        <v>10418</v>
       </c>
       <c r="D244" s="15">
         <v>72</v>
@@ -8232,208 +8169,208 @@
         <v>9</v>
       </c>
       <c r="F244" s="15">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G244" s="15">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H244" s="15">
         <v>275</v>
       </c>
       <c r="I244" s="15">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="J244" s="15">
         <v>150</v>
       </c>
       <c r="K244" s="15">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A245" s="13">
-        <v>72</v>
+      <c r="A245" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="B245" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C245" s="14">
-        <v>10418</v>
-      </c>
-      <c r="D245" s="15">
-        <v>72</v>
-      </c>
-      <c r="E245" s="15">
-        <v>9</v>
-      </c>
-      <c r="F245" s="15">
-        <v>284</v>
-      </c>
-      <c r="G245" s="15">
-        <v>234</v>
-      </c>
-      <c r="H245" s="15">
-        <v>275</v>
-      </c>
-      <c r="I245" s="15">
-        <v>400</v>
-      </c>
-      <c r="J245" s="15">
-        <v>150</v>
-      </c>
-      <c r="K245" s="15">
-        <v>50</v>
+        <v>93</v>
+      </c>
+      <c r="C245" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D245" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E245" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F245" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G245" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H245" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I245" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J245" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K245" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A246" s="9" t="s">
-        <v>181</v>
+      <c r="A246" s="13">
+        <v>73</v>
       </c>
       <c r="B246" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C246" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D246" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E246" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F246" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G246" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H246" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I246" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J246" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K246" s="29" t="s">
-        <v>181</v>
+        <v>94</v>
+      </c>
+      <c r="C246" s="14">
+        <v>11560</v>
+      </c>
+      <c r="D246" s="15">
+        <v>74</v>
+      </c>
+      <c r="E246" s="15">
+        <v>9</v>
+      </c>
+      <c r="F246" s="15">
+        <v>503</v>
+      </c>
+      <c r="G246" s="15">
+        <v>404</v>
+      </c>
+      <c r="H246" s="15">
+        <v>227</v>
+      </c>
+      <c r="I246" s="15">
+        <v>359</v>
+      </c>
+      <c r="J246" s="15">
+        <v>154</v>
+      </c>
+      <c r="K246" s="15">
+        <v>34</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A247" s="13">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B247" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C247" s="14">
-        <v>11560</v>
+        <v>11500</v>
       </c>
       <c r="D247" s="15">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E247" s="15">
         <v>9</v>
       </c>
       <c r="F247" s="15">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G247" s="15">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="H247" s="15">
-        <v>227</v>
+        <v>275</v>
       </c>
       <c r="I247" s="15">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="J247" s="15">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="K247" s="15">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A248" s="13">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B248" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C248" s="14">
-        <v>11500</v>
+        <v>10522</v>
       </c>
       <c r="D248" s="15">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E248" s="15">
         <v>9</v>
       </c>
       <c r="F248" s="15">
-        <v>500</v>
+        <v>458</v>
       </c>
       <c r="G248" s="15">
-        <v>401</v>
+        <v>367</v>
       </c>
       <c r="H248" s="15">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="I248" s="15">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="J248" s="15">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="K248" s="15">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A249" s="13">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B249" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C249" s="14">
-        <v>10522</v>
+        <v>9910</v>
       </c>
       <c r="D249" s="15">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E249" s="15">
         <v>9</v>
       </c>
       <c r="F249" s="15">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="G249" s="15">
-        <v>367</v>
+        <v>346</v>
       </c>
       <c r="H249" s="15">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="I249" s="15">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="J249" s="15">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="K249" s="15">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A250" s="13">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B250" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C250" s="14">
-        <v>9910</v>
+        <v>10889</v>
       </c>
       <c r="D250" s="15">
         <v>72</v>
@@ -8442,10 +8379,10 @@
         <v>9</v>
       </c>
       <c r="F250" s="15">
-        <v>431</v>
+        <v>474</v>
       </c>
       <c r="G250" s="15">
-        <v>346</v>
+        <v>380</v>
       </c>
       <c r="H250" s="15">
         <v>275</v>
@@ -8457,74 +8394,74 @@
         <v>150</v>
       </c>
       <c r="K250" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A251" s="13">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B251" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C251" s="14">
-        <v>10889</v>
+        <v>10522</v>
       </c>
       <c r="D251" s="15">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="E251" s="15">
         <v>9</v>
       </c>
       <c r="F251" s="15">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="G251" s="15">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="H251" s="15">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="I251" s="15">
-        <v>350</v>
+        <v>285</v>
       </c>
       <c r="J251" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K251" s="15">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A252" s="13">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B252" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C252" s="14">
-        <v>10522</v>
+        <v>10399</v>
       </c>
       <c r="D252" s="15">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E252" s="15">
         <v>9</v>
       </c>
       <c r="F252" s="15">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="G252" s="15">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="H252" s="15">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="I252" s="15">
-        <v>285</v>
+        <v>350</v>
       </c>
       <c r="J252" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K252" s="15">
         <v>31</v>
@@ -8532,13 +8469,13 @@
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A253" s="13">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B253" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C253" s="14">
-        <v>10399</v>
+        <v>10889</v>
       </c>
       <c r="D253" s="15">
         <v>72</v>
@@ -8547,10 +8484,10 @@
         <v>9</v>
       </c>
       <c r="F253" s="15">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="G253" s="15">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="H253" s="15">
         <v>275</v>
@@ -8562,18 +8499,18 @@
         <v>150</v>
       </c>
       <c r="K253" s="15">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A254" s="13">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B254" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C254" s="14">
-        <v>10889</v>
+        <v>11133</v>
       </c>
       <c r="D254" s="15">
         <v>72</v>
@@ -8582,10 +8519,10 @@
         <v>9</v>
       </c>
       <c r="F254" s="15">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="G254" s="15">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="H254" s="15">
         <v>275</v>
@@ -8597,88 +8534,88 @@
         <v>150</v>
       </c>
       <c r="K254" s="15">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A255" s="13">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B255" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C255" s="14">
-        <v>11133</v>
+        <v>10154</v>
       </c>
       <c r="D255" s="15">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E255" s="15">
         <v>9</v>
       </c>
       <c r="F255" s="15">
-        <v>484</v>
+        <v>442</v>
       </c>
       <c r="G255" s="15">
-        <v>389</v>
+        <v>354</v>
       </c>
       <c r="H255" s="15">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="I255" s="15">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="J255" s="15">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="K255" s="15">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A256" s="13">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B256" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C256" s="14">
-        <v>10154</v>
+        <v>10277</v>
       </c>
       <c r="D256" s="15">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E256" s="15">
         <v>9</v>
       </c>
       <c r="F256" s="15">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="G256" s="15">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="H256" s="15">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="I256" s="15">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="J256" s="15">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="K256" s="15">
         <v>30</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A257" s="13">
-        <v>83</v>
+      <c r="A257" s="16">
+        <v>84</v>
       </c>
       <c r="B257" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C257" s="14">
-        <v>10277</v>
+        <v>10766</v>
       </c>
       <c r="D257" s="15">
         <v>72</v>
@@ -8687,13 +8624,13 @@
         <v>9</v>
       </c>
       <c r="F257" s="15">
-        <v>447</v>
+        <v>469</v>
       </c>
       <c r="G257" s="15">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="H257" s="15">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="I257" s="15">
         <v>350</v>
@@ -8702,88 +8639,88 @@
         <v>150</v>
       </c>
       <c r="K257" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A258" s="16">
-        <v>84</v>
+      <c r="A258" s="13">
+        <v>85</v>
       </c>
       <c r="B258" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C258" s="14">
-        <v>10766</v>
+        <v>10277</v>
       </c>
       <c r="D258" s="15">
         <v>72</v>
       </c>
       <c r="E258" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F258" s="15">
-        <v>469</v>
+        <v>447</v>
       </c>
       <c r="G258" s="15">
-        <v>376</v>
+        <v>448</v>
       </c>
       <c r="H258" s="15">
-        <v>211</v>
+        <v>275</v>
       </c>
       <c r="I258" s="15">
-        <v>350</v>
+        <v>534</v>
       </c>
       <c r="J258" s="15">
         <v>150</v>
       </c>
       <c r="K258" s="15">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259" s="13">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B259" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C259" s="14">
-        <v>10277</v>
+        <v>10889</v>
       </c>
       <c r="D259" s="15">
         <v>72</v>
       </c>
       <c r="E259" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F259" s="15">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="G259" s="15">
-        <v>448</v>
+        <v>380</v>
       </c>
       <c r="H259" s="15">
         <v>275</v>
       </c>
       <c r="I259" s="15">
-        <v>534</v>
+        <v>350</v>
       </c>
       <c r="J259" s="15">
         <v>150</v>
       </c>
       <c r="K259" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A260" s="13">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B260" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C260" s="14">
-        <v>10889</v>
+        <v>11133</v>
       </c>
       <c r="D260" s="15">
         <v>72</v>
@@ -8792,10 +8729,10 @@
         <v>9</v>
       </c>
       <c r="F260" s="15">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="G260" s="15">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="H260" s="15">
         <v>275</v>
@@ -8807,88 +8744,88 @@
         <v>150</v>
       </c>
       <c r="K260" s="15">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A261" s="13">
-        <v>87</v>
+      <c r="A261" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="B261" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C261" s="14">
-        <v>11133</v>
-      </c>
-      <c r="D261" s="15">
-        <v>72</v>
-      </c>
-      <c r="E261" s="15">
-        <v>9</v>
-      </c>
-      <c r="F261" s="15">
-        <v>484</v>
-      </c>
-      <c r="G261" s="15">
-        <v>389</v>
-      </c>
-      <c r="H261" s="15">
-        <v>275</v>
-      </c>
-      <c r="I261" s="15">
-        <v>350</v>
-      </c>
-      <c r="J261" s="15">
-        <v>150</v>
-      </c>
-      <c r="K261" s="15">
-        <v>33</v>
+        <v>109</v>
+      </c>
+      <c r="C261" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D261" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E261" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F261" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G261" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H261" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I261" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J261" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K261" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A262" s="9" t="s">
-        <v>181</v>
+      <c r="A262" s="13">
+        <v>88</v>
       </c>
       <c r="B262" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C262" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D262" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E262" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F262" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G262" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H262" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I262" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J262" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K262" s="29" t="s">
-        <v>181</v>
+        <v>110</v>
+      </c>
+      <c r="C262" s="14">
+        <v>10399</v>
+      </c>
+      <c r="D262" s="15">
+        <v>63</v>
+      </c>
+      <c r="E262" s="15">
+        <v>9</v>
+      </c>
+      <c r="F262" s="15">
+        <v>453</v>
+      </c>
+      <c r="G262" s="15">
+        <v>363</v>
+      </c>
+      <c r="H262" s="15">
+        <v>250</v>
+      </c>
+      <c r="I262" s="15">
+        <v>300</v>
+      </c>
+      <c r="J262" s="15">
+        <v>125</v>
+      </c>
+      <c r="K262" s="15">
+        <v>31</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A263" s="13">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B263" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C263" s="14">
-        <v>10399</v>
+        <v>11256</v>
       </c>
       <c r="D263" s="15">
         <v>63</v>
@@ -8897,10 +8834,10 @@
         <v>9</v>
       </c>
       <c r="F263" s="15">
-        <v>453</v>
+        <v>490</v>
       </c>
       <c r="G263" s="15">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="H263" s="15">
         <v>250</v>
@@ -8912,18 +8849,18 @@
         <v>125</v>
       </c>
       <c r="K263" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A264" s="13">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B264" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C264" s="14">
-        <v>11256</v>
+        <v>11990</v>
       </c>
       <c r="D264" s="15">
         <v>63</v>
@@ -8932,10 +8869,10 @@
         <v>9</v>
       </c>
       <c r="F264" s="15">
-        <v>490</v>
+        <v>522</v>
       </c>
       <c r="G264" s="15">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="H264" s="15">
         <v>250</v>
@@ -8947,91 +8884,91 @@
         <v>125</v>
       </c>
       <c r="K264" s="15">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A265" s="13">
-        <v>90</v>
+      <c r="A265" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="B265" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C265" s="14">
-        <v>11990</v>
-      </c>
-      <c r="D265" s="15">
-        <v>63</v>
-      </c>
-      <c r="E265" s="15">
-        <v>9</v>
-      </c>
-      <c r="F265" s="15">
-        <v>522</v>
-      </c>
-      <c r="G265" s="15">
-        <v>419</v>
-      </c>
-      <c r="H265" s="15">
-        <v>250</v>
-      </c>
-      <c r="I265" s="15">
-        <v>300</v>
-      </c>
-      <c r="J265" s="15">
-        <v>125</v>
-      </c>
-      <c r="K265" s="15">
-        <v>35</v>
+        <v>113</v>
+      </c>
+      <c r="C265" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D265" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E265" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F265" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G265" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H265" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I265" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J265" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K265" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A266" s="9" t="s">
-        <v>181</v>
+      <c r="A266" s="13">
+        <v>91</v>
       </c>
       <c r="B266" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C266" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D266" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E266" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F266" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G266" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H266" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I266" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J266" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K266" s="29" t="s">
-        <v>181</v>
+        <v>114</v>
+      </c>
+      <c r="C266" s="14">
+        <v>9905</v>
+      </c>
+      <c r="D266" s="15">
+        <v>72</v>
+      </c>
+      <c r="E266" s="15">
+        <v>9</v>
+      </c>
+      <c r="F266" s="15">
+        <v>371</v>
+      </c>
+      <c r="G266" s="15">
+        <v>397</v>
+      </c>
+      <c r="H266" s="15">
+        <v>441</v>
+      </c>
+      <c r="I266" s="15">
+        <v>397</v>
+      </c>
+      <c r="J266" s="15">
+        <v>309</v>
+      </c>
+      <c r="K266" s="15">
+        <v>20</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A267" s="13">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B267" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C267" s="14">
         <v>9905</v>
       </c>
       <c r="D267" s="15">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E267" s="15">
         <v>9</v>
@@ -9046,7 +8983,7 @@
         <v>441</v>
       </c>
       <c r="I267" s="15">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="J267" s="15">
         <v>309</v>
@@ -9057,13 +8994,13 @@
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A268" s="13">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B268" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C268" s="14">
-        <v>9905</v>
+        <v>10863</v>
       </c>
       <c r="D268" s="15">
         <v>80</v>
@@ -9072,30 +9009,30 @@
         <v>9</v>
       </c>
       <c r="F268" s="15">
-        <v>371</v>
+        <v>407</v>
       </c>
       <c r="G268" s="15">
-        <v>397</v>
+        <v>436</v>
       </c>
       <c r="H268" s="15">
-        <v>441</v>
+        <v>484</v>
       </c>
       <c r="I268" s="15">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="J268" s="15">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="K268" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A269" s="13">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B269" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C269" s="14">
         <v>10863</v>
@@ -9127,69 +9064,69 @@
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A270" s="13">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B270" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C270" s="14">
-        <v>10863</v>
+        <v>10437</v>
       </c>
       <c r="D270" s="15">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E270" s="15">
         <v>9</v>
       </c>
       <c r="F270" s="15">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="G270" s="15">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="H270" s="15">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="I270" s="15">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="J270" s="15">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="K270" s="15">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A271" s="13">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B271" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C271" s="14">
-        <v>10437</v>
+        <v>10331</v>
       </c>
       <c r="D271" s="15">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E271" s="15">
         <v>9</v>
       </c>
       <c r="F271" s="15">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="G271" s="15">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="H271" s="15">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="I271" s="15">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="J271" s="15">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="K271" s="15">
         <v>21</v>
@@ -9197,45 +9134,45 @@
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A272" s="13">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B272" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C272" s="14">
-        <v>10331</v>
+        <v>9905</v>
       </c>
       <c r="D272" s="15">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E272" s="15">
         <v>9</v>
       </c>
       <c r="F272" s="15">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="G272" s="15">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="H272" s="15">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="I272" s="15">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="J272" s="15">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="K272" s="15">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A273" s="13">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B273" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C273" s="14">
         <v>9905</v>
@@ -9266,154 +9203,154 @@
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A274" s="13">
-        <v>98</v>
+      <c r="A274" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="B274" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="C274" s="14">
-        <v>9905</v>
-      </c>
-      <c r="D274" s="15">
-        <v>72</v>
-      </c>
-      <c r="E274" s="15">
-        <v>9</v>
-      </c>
-      <c r="F274" s="15">
-        <v>371</v>
-      </c>
-      <c r="G274" s="15">
-        <v>397</v>
-      </c>
-      <c r="H274" s="15">
-        <v>441</v>
-      </c>
-      <c r="I274" s="15">
-        <v>397</v>
-      </c>
-      <c r="J274" s="15">
-        <v>309</v>
-      </c>
-      <c r="K274" s="15">
-        <v>20</v>
+        <v>122</v>
+      </c>
+      <c r="C274" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D274" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E274" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F274" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G274" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H274" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I274" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J274" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K274" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A275" s="9" t="s">
-        <v>181</v>
+      <c r="A275" s="13">
+        <v>99</v>
       </c>
       <c r="B275" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C275" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D275" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E275" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F275" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G275" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H275" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I275" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J275" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K275" s="29" t="s">
-        <v>181</v>
+        <v>123</v>
+      </c>
+      <c r="C275" s="14">
+        <v>9197</v>
+      </c>
+      <c r="D275" s="15">
+        <v>55</v>
+      </c>
+      <c r="E275" s="15">
+        <v>9</v>
+      </c>
+      <c r="F275" s="15">
+        <v>321</v>
+      </c>
+      <c r="G275" s="15">
+        <v>149</v>
+      </c>
+      <c r="H275" s="15">
+        <v>575</v>
+      </c>
+      <c r="I275" s="15">
+        <v>885</v>
+      </c>
+      <c r="J275" s="19">
+        <v>2.7669999999999999</v>
+      </c>
+      <c r="K275" s="15">
+        <v>28</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A276" s="13">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B276" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C276" s="14">
-        <v>9197</v>
+        <v>11400</v>
       </c>
       <c r="D276" s="15">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="E276" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F276" s="15">
-        <v>321</v>
+        <v>400</v>
       </c>
       <c r="G276" s="15">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="H276" s="15">
-        <v>575</v>
-      </c>
-      <c r="I276" s="15">
-        <v>885</v>
-      </c>
-      <c r="J276" s="27">
-        <v>2.7669999999999999</v>
+        <v>710</v>
+      </c>
+      <c r="I276" s="19">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J276" s="14">
+        <v>2563</v>
       </c>
       <c r="K276" s="15">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A277" s="13">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B277" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C277" s="14">
-        <v>11400</v>
+        <v>8132</v>
       </c>
       <c r="D277" s="15">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="E277" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F277" s="15">
-        <v>400</v>
+        <v>284</v>
       </c>
       <c r="G277" s="15">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="H277" s="15">
-        <v>710</v>
-      </c>
-      <c r="I277" s="27">
-        <v>1.1000000000000001</v>
+        <v>509</v>
+      </c>
+      <c r="I277" s="15">
+        <v>783</v>
       </c>
       <c r="J277" s="14">
-        <v>2563</v>
+        <v>2446</v>
       </c>
       <c r="K277" s="15">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A278" s="13">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B278" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C278" s="14">
-        <v>8132</v>
+        <v>8229</v>
       </c>
       <c r="D278" s="15">
         <v>63</v>
@@ -9422,19 +9359,19 @@
         <v>9</v>
       </c>
       <c r="F278" s="15">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G278" s="15">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H278" s="15">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="I278" s="15">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="J278" s="14">
-        <v>2446</v>
+        <v>2475</v>
       </c>
       <c r="K278" s="15">
         <v>25</v>
@@ -9442,16 +9379,16 @@
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A279" s="13">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B279" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C279" s="14">
         <v>8229</v>
       </c>
       <c r="D279" s="15">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E279" s="15">
         <v>9</v>
@@ -9477,10 +9414,10 @@
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A280" s="13">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B280" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C280" s="14">
         <v>8229</v>
@@ -9512,34 +9449,34 @@
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A281" s="13">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B281" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C281" s="14">
-        <v>8229</v>
+        <v>8423</v>
       </c>
       <c r="D281" s="15">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E281" s="15">
         <v>9</v>
       </c>
       <c r="F281" s="15">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="G281" s="15">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H281" s="15">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="I281" s="15">
-        <v>792</v>
+        <v>811</v>
       </c>
       <c r="J281" s="14">
-        <v>2475</v>
+        <v>2534</v>
       </c>
       <c r="K281" s="15">
         <v>25</v>
@@ -9547,10 +9484,10 @@
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A282" s="13">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B282" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C282" s="14">
         <v>8423</v>
@@ -9581,81 +9518,81 @@
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A283" s="13">
-        <v>106</v>
+      <c r="A283" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="B283" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C283" s="14">
-        <v>8423</v>
-      </c>
-      <c r="D283" s="15">
+        <v>131</v>
+      </c>
+      <c r="C283" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D283" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E283" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F283" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G283" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H283" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I283" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J283" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K283" s="21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A284" s="13">
+        <v>107</v>
+      </c>
+      <c r="B284" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C284" s="14">
+        <v>8617</v>
+      </c>
+      <c r="D284" s="15">
         <v>63</v>
       </c>
-      <c r="E283" s="15">
-        <v>9</v>
-      </c>
-      <c r="F283" s="15">
-        <v>294</v>
-      </c>
-      <c r="G283" s="15">
-        <v>137</v>
-      </c>
-      <c r="H283" s="15">
-        <v>527</v>
-      </c>
-      <c r="I283" s="15">
-        <v>811</v>
-      </c>
-      <c r="J283" s="14">
-        <v>2534</v>
-      </c>
-      <c r="K283" s="15">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A284" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="B284" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="C284" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D284" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E284" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F284" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G284" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H284" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I284" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J284" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K284" s="29" t="s">
-        <v>181</v>
+      <c r="E284" s="15">
+        <v>9</v>
+      </c>
+      <c r="F284" s="15">
+        <v>301</v>
+      </c>
+      <c r="G284" s="15">
+        <v>140</v>
+      </c>
+      <c r="H284" s="15">
+        <v>539</v>
+      </c>
+      <c r="I284" s="15">
+        <v>829</v>
+      </c>
+      <c r="J284" s="14">
+        <v>2592</v>
+      </c>
+      <c r="K284" s="15">
+        <v>26</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A285" s="13">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B285" s="11" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="C285" s="14">
         <v>8617</v>
@@ -9687,10 +9624,10 @@
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A286" s="13">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B286" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C286" s="14">
         <v>8617</v>
@@ -9722,13 +9659,13 @@
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A287" s="13">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B287" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C287" s="14">
-        <v>8617</v>
+        <v>8423</v>
       </c>
       <c r="D287" s="15">
         <v>63</v>
@@ -9737,30 +9674,30 @@
         <v>9</v>
       </c>
       <c r="F287" s="15">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="G287" s="15">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H287" s="15">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="I287" s="15">
-        <v>829</v>
+        <v>811</v>
       </c>
       <c r="J287" s="14">
-        <v>2592</v>
+        <v>2534</v>
       </c>
       <c r="K287" s="15">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A288" s="13">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B288" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C288" s="14">
         <v>8423</v>
@@ -9792,13 +9729,13 @@
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289" s="13">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B289" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C289" s="14">
-        <v>8423</v>
+        <v>7500</v>
       </c>
       <c r="D289" s="15">
         <v>63</v>
@@ -9807,30 +9744,30 @@
         <v>9</v>
       </c>
       <c r="F289" s="15">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="G289" s="15">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="H289" s="15">
-        <v>527</v>
+        <v>430</v>
       </c>
       <c r="I289" s="15">
-        <v>811</v>
+        <v>662</v>
       </c>
       <c r="J289" s="14">
-        <v>2534</v>
+        <v>2068</v>
       </c>
       <c r="K289" s="15">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290" s="13">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B290" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C290" s="14">
         <v>7500</v>
@@ -9862,10 +9799,10 @@
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A291" s="13">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B291" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C291" s="14">
         <v>7500</v>
@@ -9897,13 +9834,13 @@
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292" s="13">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B292" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C292" s="14">
-        <v>7500</v>
+        <v>8617</v>
       </c>
       <c r="D292" s="15">
         <v>63</v>
@@ -9912,33 +9849,33 @@
         <v>9</v>
       </c>
       <c r="F292" s="15">
-        <v>240</v>
+        <v>301</v>
       </c>
       <c r="G292" s="15">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="H292" s="15">
-        <v>430</v>
+        <v>539</v>
       </c>
       <c r="I292" s="15">
-        <v>662</v>
+        <v>829</v>
       </c>
       <c r="J292" s="14">
-        <v>2068</v>
+        <v>2592</v>
       </c>
       <c r="K292" s="15">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293" s="13">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B293" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C293" s="14">
-        <v>8617</v>
+        <v>7500</v>
       </c>
       <c r="D293" s="15">
         <v>63</v>
@@ -9947,138 +9884,138 @@
         <v>9</v>
       </c>
       <c r="F293" s="15">
-        <v>301</v>
+        <v>240</v>
       </c>
       <c r="G293" s="15">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="H293" s="15">
-        <v>539</v>
+        <v>430</v>
       </c>
       <c r="I293" s="15">
-        <v>829</v>
+        <v>662</v>
       </c>
       <c r="J293" s="14">
-        <v>2592</v>
+        <v>2068</v>
       </c>
       <c r="K293" s="15">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A294" s="13">
+        <v>117</v>
+      </c>
+      <c r="B294" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C294" s="14">
+        <v>7164</v>
+      </c>
+      <c r="D294" s="15">
+        <v>72</v>
+      </c>
+      <c r="E294" s="15">
+        <v>9</v>
+      </c>
+      <c r="F294" s="15">
+        <v>250</v>
+      </c>
+      <c r="G294" s="15">
         <v>116</v>
       </c>
-      <c r="B294" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C294" s="14">
-        <v>7500</v>
-      </c>
-      <c r="D294" s="15">
-        <v>63</v>
-      </c>
-      <c r="E294" s="15">
-        <v>9</v>
-      </c>
-      <c r="F294" s="15">
-        <v>240</v>
-      </c>
-      <c r="G294" s="15">
-        <v>112</v>
-      </c>
       <c r="H294" s="15">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I294" s="15">
-        <v>662</v>
+        <v>690</v>
       </c>
       <c r="J294" s="14">
-        <v>2068</v>
+        <v>2155</v>
       </c>
       <c r="K294" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A295" s="13">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B295" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C295" s="14">
-        <v>7164</v>
+        <v>9004</v>
       </c>
       <c r="D295" s="15">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E295" s="15">
         <v>9</v>
       </c>
       <c r="F295" s="15">
-        <v>250</v>
+        <v>314</v>
       </c>
       <c r="G295" s="15">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="H295" s="15">
-        <v>448</v>
+        <v>563</v>
       </c>
       <c r="I295" s="15">
-        <v>690</v>
+        <v>867</v>
       </c>
       <c r="J295" s="14">
-        <v>2155</v>
+        <v>2708</v>
       </c>
       <c r="K295" s="15">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A296" s="13">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B296" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C296" s="14">
-        <v>9004</v>
+        <v>8617</v>
       </c>
       <c r="D296" s="15">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E296" s="15">
         <v>9</v>
       </c>
       <c r="F296" s="15">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="G296" s="15">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="H296" s="15">
-        <v>563</v>
+        <v>539</v>
       </c>
       <c r="I296" s="15">
-        <v>867</v>
+        <v>829</v>
       </c>
       <c r="J296" s="14">
-        <v>2708</v>
+        <v>2592</v>
       </c>
       <c r="K296" s="15">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A297" s="13">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B297" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C297" s="14">
-        <v>8617</v>
+        <v>8520</v>
       </c>
       <c r="D297" s="15">
         <v>72</v>
@@ -10087,19 +10024,19 @@
         <v>9</v>
       </c>
       <c r="F297" s="15">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="G297" s="15">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H297" s="15">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="I297" s="15">
-        <v>829</v>
+        <v>820</v>
       </c>
       <c r="J297" s="14">
-        <v>2592</v>
+        <v>2563</v>
       </c>
       <c r="K297" s="15">
         <v>26</v>
@@ -10107,34 +10044,34 @@
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A298" s="13">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B298" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C298" s="14">
-        <v>8520</v>
+        <v>8617</v>
       </c>
       <c r="D298" s="15">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E298" s="15">
         <v>9</v>
       </c>
       <c r="F298" s="15">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G298" s="15">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H298" s="15">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="I298" s="15">
-        <v>820</v>
+        <v>829</v>
       </c>
       <c r="J298" s="14">
-        <v>2563</v>
+        <v>2592</v>
       </c>
       <c r="K298" s="15">
         <v>26</v>
@@ -10142,13 +10079,13 @@
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A299" s="13">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B299" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C299" s="14">
-        <v>8617</v>
+        <v>7500</v>
       </c>
       <c r="D299" s="15">
         <v>63</v>
@@ -10157,30 +10094,30 @@
         <v>9</v>
       </c>
       <c r="F299" s="15">
-        <v>301</v>
+        <v>240</v>
       </c>
       <c r="G299" s="15">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="H299" s="15">
-        <v>539</v>
+        <v>430</v>
       </c>
       <c r="I299" s="15">
-        <v>829</v>
+        <v>662</v>
       </c>
       <c r="J299" s="14">
-        <v>2592</v>
+        <v>2068</v>
       </c>
       <c r="K299" s="15">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A300" s="13">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B300" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C300" s="14">
         <v>7500</v>
@@ -10211,81 +10148,81 @@
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A301" s="13">
-        <v>123</v>
+      <c r="A301" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="B301" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="C301" s="14">
-        <v>7500</v>
-      </c>
-      <c r="D301" s="15">
-        <v>63</v>
-      </c>
-      <c r="E301" s="15">
-        <v>9</v>
-      </c>
-      <c r="F301" s="15">
-        <v>240</v>
-      </c>
-      <c r="G301" s="15">
-        <v>112</v>
-      </c>
-      <c r="H301" s="15">
-        <v>430</v>
-      </c>
-      <c r="I301" s="15">
-        <v>662</v>
-      </c>
-      <c r="J301" s="14">
-        <v>2068</v>
-      </c>
-      <c r="K301" s="15">
-        <v>21</v>
+        <v>149</v>
+      </c>
+      <c r="C301" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D301" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E301" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F301" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G301" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H301" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I301" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J301" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K301" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A302" s="9" t="s">
-        <v>181</v>
+      <c r="A302" s="13">
+        <v>124</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="C302" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D302" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="E302" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="F302" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G302" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H302" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I302" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="J302" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="K302" s="29" t="s">
-        <v>181</v>
+        <v>150</v>
+      </c>
+      <c r="C302" s="14">
+        <v>9585</v>
+      </c>
+      <c r="D302" s="15">
+        <v>72</v>
+      </c>
+      <c r="E302" s="15">
+        <v>9</v>
+      </c>
+      <c r="F302" s="15">
+        <v>334</v>
+      </c>
+      <c r="G302" s="15">
+        <v>200</v>
+      </c>
+      <c r="H302" s="15">
+        <v>600</v>
+      </c>
+      <c r="I302" s="15">
+        <v>923</v>
+      </c>
+      <c r="J302" s="14">
+        <v>2883</v>
+      </c>
+      <c r="K302" s="15">
+        <v>29</v>
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303" s="13">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B303" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C303" s="14">
         <v>9585</v>
@@ -10300,7 +10237,7 @@
         <v>334</v>
       </c>
       <c r="G303" s="15">
-        <v>200</v>
+        <v>156</v>
       </c>
       <c r="H303" s="15">
         <v>600</v>
@@ -10317,10 +10254,10 @@
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304" s="13">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B304" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C304" s="14">
         <v>9585</v>
@@ -10352,13 +10289,13 @@
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A305" s="13">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B305" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C305" s="14">
-        <v>9585</v>
+        <v>10359</v>
       </c>
       <c r="D305" s="15">
         <v>72</v>
@@ -10367,33 +10304,33 @@
         <v>9</v>
       </c>
       <c r="F305" s="15">
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="G305" s="15">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="H305" s="15">
-        <v>600</v>
+        <v>648</v>
       </c>
       <c r="I305" s="15">
-        <v>923</v>
+        <v>997</v>
       </c>
       <c r="J305" s="14">
-        <v>2883</v>
+        <v>3116</v>
       </c>
       <c r="K305" s="15">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A306" s="13">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B306" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C306" s="14">
-        <v>10359</v>
+        <v>9585</v>
       </c>
       <c r="D306" s="15">
         <v>72</v>
@@ -10402,33 +10339,33 @@
         <v>9</v>
       </c>
       <c r="F306" s="15">
-        <v>361</v>
+        <v>334</v>
       </c>
       <c r="G306" s="15">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H306" s="15">
-        <v>648</v>
+        <v>600</v>
       </c>
       <c r="I306" s="15">
-        <v>997</v>
+        <v>923</v>
       </c>
       <c r="J306" s="14">
-        <v>3116</v>
+        <v>2883</v>
       </c>
       <c r="K306" s="15">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A307" s="13">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B307" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C307" s="14">
-        <v>9585</v>
+        <v>9200</v>
       </c>
       <c r="D307" s="15">
         <v>72</v>
@@ -10437,33 +10374,33 @@
         <v>9</v>
       </c>
       <c r="F307" s="15">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="G307" s="15">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H307" s="15">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="I307" s="15">
-        <v>923</v>
+        <v>885</v>
       </c>
       <c r="J307" s="14">
-        <v>2883</v>
+        <v>2767</v>
       </c>
       <c r="K307" s="15">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A308" s="13">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B308" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C308" s="14">
-        <v>9200</v>
+        <v>9585</v>
       </c>
       <c r="D308" s="15">
         <v>72</v>
@@ -10472,33 +10409,33 @@
         <v>9</v>
       </c>
       <c r="F308" s="15">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="G308" s="15">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="H308" s="15">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="I308" s="15">
-        <v>885</v>
+        <v>923</v>
       </c>
       <c r="J308" s="14">
-        <v>2767</v>
+        <v>2883</v>
       </c>
       <c r="K308" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A309" s="13">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B309" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C309" s="14">
-        <v>9585</v>
+        <v>9197</v>
       </c>
       <c r="D309" s="15">
         <v>72</v>
@@ -10507,33 +10444,33 @@
         <v>9</v>
       </c>
       <c r="F309" s="15">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="G309" s="15">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H309" s="15">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="I309" s="15">
         <v>923</v>
       </c>
       <c r="J309" s="14">
-        <v>2883</v>
+        <v>2767</v>
       </c>
       <c r="K309" s="15">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A310" s="13">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B310" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C310" s="14">
-        <v>9197</v>
+        <v>9585</v>
       </c>
       <c r="D310" s="15">
         <v>72</v>
@@ -10542,33 +10479,33 @@
         <v>9</v>
       </c>
       <c r="F310" s="15">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="G310" s="15">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="H310" s="15">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="I310" s="15">
         <v>923</v>
       </c>
       <c r="J310" s="14">
-        <v>2767</v>
+        <v>2883</v>
       </c>
       <c r="K310" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A311" s="13">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B311" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C311" s="14">
-        <v>9585</v>
+        <v>8907</v>
       </c>
       <c r="D311" s="15">
         <v>72</v>
@@ -10577,33 +10514,33 @@
         <v>9</v>
       </c>
       <c r="F311" s="15">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="G311" s="15">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="H311" s="15">
-        <v>600</v>
+        <v>557</v>
       </c>
       <c r="I311" s="15">
-        <v>923</v>
+        <v>857</v>
       </c>
       <c r="J311" s="14">
-        <v>2883</v>
+        <v>2679</v>
       </c>
       <c r="K311" s="15">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A312" s="13">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B312" s="11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C312" s="14">
-        <v>8907</v>
+        <v>9101</v>
       </c>
       <c r="D312" s="15">
         <v>72</v>
@@ -10612,69 +10549,25 @@
         <v>9</v>
       </c>
       <c r="F312" s="15">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G312" s="15">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H312" s="15">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="I312" s="15">
-        <v>857</v>
+        <v>876</v>
       </c>
       <c r="J312" s="14">
-        <v>2679</v>
+        <v>2737</v>
       </c>
       <c r="K312" s="15">
         <v>27</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A313" s="13">
-        <v>134</v>
-      </c>
-      <c r="B313" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C313" s="14">
-        <v>9101</v>
-      </c>
-      <c r="D313" s="15">
-        <v>72</v>
-      </c>
-      <c r="E313" s="15">
-        <v>9</v>
-      </c>
-      <c r="F313" s="15">
-        <v>318</v>
-      </c>
-      <c r="G313" s="15">
-        <v>148</v>
-      </c>
-      <c r="H313" s="15">
-        <v>569</v>
-      </c>
-      <c r="I313" s="15">
-        <v>876</v>
-      </c>
-      <c r="J313" s="14">
-        <v>2737</v>
-      </c>
-      <c r="K313" s="15">
-        <v>27</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="K160:K161"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="C160:E160"/>
-    <mergeCell ref="F160:F161"/>
-    <mergeCell ref="G160:G161"/>
-    <mergeCell ref="H160:J160"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>